--- a/04_DESIGN_TABLES/DesignTable_5000.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_5000.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1610,24 +1615,47 @@
           <t>5000-06-02</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.405</v>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>5000-06-02</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3/8-18 x 1/8-27 NPTF (female both ends)</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-06-02 col "L LGTH" = "1.130" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 430.3, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; CHEX@HEX: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-06-02 col "C HEX" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 430.3, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL1@BORE: end library gen_straight2 FPT[6] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.57, FPT_P1 0.68 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 3/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[6] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; TAPDRILL2@BORE: end library gen_straight2 FPT[2] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.33, FPT_P1 0.46 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/8 NPT basic dimensions = tools_new/generators/ms51500.NPTF[2] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread texts from the part-number dashes (NPTF lib), format of the built 5000 rows</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; tap drills = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1638,6 +1666,11 @@
       <c r="N22" t="inlineStr">
         <is>
           <t>5000-06-02</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1647,24 +1680,47 @@
           <t>5000-16-08</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.84</v>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>5000-16-08</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1-11 1/2 x 1/2-14 NPTF (female both ends)</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L@DRIVE: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-16-08 col "L LGTH" = "1.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 551.2, page verified) [Brennan = yes 2026-10-18] - overall length; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; CHEX@HEX: Brennan TFA catalog p10 table TFA-p010-t04 "5000 FP-FP STRAIGHT" row 5000-16-08 col "C HEX" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 551.2, page verified) [Brennan = yes 2026-10-18] - body hex; mapping: TFA p10 5000 drawing: L = overall, C HEX = body hex (impact/F2a.json, certain); same-table check on today's base: 19/19 rows with an Air-Way/OMi value agree with this catalog column to rounding; TAPDRILL1@BORE: end library gen_straight2 FPT[16] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 1.14, FPT_P1 1.14 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A1@DRIVE: end library: ASME B1.20.1 / B1.20.3 1 NPT basic dimensions = tools_new/generators/ms51500.NPTF[16] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; TAPDRILL2@BORE: end library gen_straight2 FPT[8] (= tools_new/generators/templates/DesignTable_2405_SW2.xlsx row of that pipe dash: TAPDRILL@BORE_A 0.7, FPT_P1 0.9 = MS51503 P1 max) = Air-Way per-size tap drill (-02 0.33 ... -20 1.48) [user 2026-10-18 A1 Q-TRANSFER-TAPDRILL yes, 00_DOCS/ANSWERS_2026-10-18.md]; THDMAJ_A2@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/2 NPT basic dimensions = tools_new/generators/ms51500.NPTF[8] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; $PRP@Threads: thread texts from the part-number dashes (NPTF lib), format of the built 5000 rows</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; tap drills = Air-Way per size (A1 yes)</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1675,6 +1731,11 @@
       <c r="N23" t="inlineStr">
         <is>
           <t>5000-16-08</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1721,24 +1782,47 @@
           <t>5000-40-40</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="C25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.729</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.875</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.875</v>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>5000-40-40</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2 1/2-8 x 2 1/2-8 NPTF (female both ends)</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but the Air-Way page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L / hex from the Brennan TFA catalog p10 alone; -40 pipe ends not in the end library</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1749,6 +1833,11 @@
       <c r="N25" t="inlineStr">
         <is>
           <t>5000-40-40</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
